--- a/artfynd/A 18098-2024 artfynd.xlsx
+++ b/artfynd/A 18098-2024 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>134266572</v>
       </c>
       <c r="B6" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>134266290</v>
       </c>
       <c r="B7" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>134267874</v>
       </c>
       <c r="B8" t="n">
-        <v>79383</v>
+        <v>79390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>134267359</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>134267296</v>
       </c>
       <c r="B10" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>134267700</v>
       </c>
       <c r="B11" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>134267735</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>134267335</v>
       </c>
       <c r="B13" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>134267687</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>134273538</v>
       </c>
       <c r="B15" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>134273565</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>134273567</v>
       </c>
       <c r="B17" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>134267152</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>134273542</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>134273573</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 18098-2024 artfynd.xlsx
+++ b/artfynd/A 18098-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117398714</v>
+        <v>134266572</v>
       </c>
       <c r="B2" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>967</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520889</v>
+        <v>520844</v>
       </c>
       <c r="R2" t="n">
-        <v>6847678</v>
+        <v>6847711</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117398799</v>
+        <v>117398705</v>
       </c>
       <c r="B3" t="n">
-        <v>78216</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +814,7 @@
         <v>520859</v>
       </c>
       <c r="R3" t="n">
-        <v>6847728</v>
+        <v>6847729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,12 +881,7 @@
         <v>117398708</v>
       </c>
       <c r="B4" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117398705</v>
+        <v>117398714</v>
       </c>
       <c r="B5" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520859</v>
+        <v>520889</v>
       </c>
       <c r="R5" t="n">
-        <v>6847729</v>
+        <v>6847678</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134266572</v>
+        <v>134267152</v>
       </c>
       <c r="B6" t="n">
-        <v>97428</v>
+        <v>79468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520844</v>
+        <v>520881</v>
       </c>
       <c r="R6" t="n">
-        <v>6847711</v>
+        <v>6847688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,6 +1161,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på grov gammal silverhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134266290</v>
+        <v>134267700</v>
       </c>
       <c r="B7" t="n">
-        <v>79956</v>
+        <v>79468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520788</v>
+        <v>520903</v>
       </c>
       <c r="R7" t="n">
-        <v>6847808</v>
+        <v>6847766</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,48 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134267874</v>
+        <v>134273537</v>
       </c>
       <c r="B8" t="n">
-        <v>79390</v>
+        <v>79468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>967</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520826</v>
+        <v>520751</v>
       </c>
       <c r="R8" t="n">
-        <v>6847798</v>
+        <v>6847771</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,9 +1357,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,22 +1384,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134267359</v>
+        <v>134273538</v>
       </c>
       <c r="B9" t="n">
-        <v>79123</v>
+        <v>79468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,37 +1407,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520900</v>
+        <v>520765</v>
       </c>
       <c r="R9" t="n">
-        <v>6847679</v>
+        <v>6847748</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,9 +1464,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,22 +1491,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134267296</v>
+        <v>134273542</v>
       </c>
       <c r="B10" t="n">
-        <v>79956</v>
+        <v>79468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,37 +1514,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520886</v>
+        <v>520761</v>
       </c>
       <c r="R10" t="n">
-        <v>6847676</v>
+        <v>6847669</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1575,9 +1571,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,22 +1598,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134267700</v>
+        <v>134273564</v>
       </c>
       <c r="B11" t="n">
-        <v>79461</v>
+        <v>79468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,17 +1641,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520903</v>
+        <v>520960</v>
       </c>
       <c r="R11" t="n">
-        <v>6847766</v>
+        <v>6847685</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,9 +1678,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,22 +1705,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134267735</v>
+        <v>134273565</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,37 +1728,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520889</v>
+        <v>520959</v>
       </c>
       <c r="R12" t="n">
-        <v>6847776</v>
+        <v>6847697</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1769,9 +1785,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,22 +1812,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134267335</v>
+        <v>134273567</v>
       </c>
       <c r="B13" t="n">
-        <v>79985</v>
+        <v>79468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,37 +1835,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520898</v>
+        <v>520974</v>
       </c>
       <c r="R13" t="n">
-        <v>6847679</v>
+        <v>6847722</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1866,9 +1892,24 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Högstubbe med kulturspår och varglav.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1883,26 +1924,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134267687</v>
+        <v>134267652</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1930,13 +1971,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520899</v>
+        <v>520975</v>
       </c>
       <c r="R14" t="n">
-        <v>6847741</v>
+        <v>6847726</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,48 +2033,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134273538</v>
+        <v>134267687</v>
       </c>
       <c r="B15" t="n">
-        <v>79461</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520765</v>
+        <v>520899</v>
       </c>
       <c r="R15" t="n">
-        <v>6847748</v>
+        <v>6847741</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2060,19 +2101,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:37</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,60 +2118,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134273565</v>
+        <v>134267735</v>
       </c>
       <c r="B16" t="n">
-        <v>79461</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520959</v>
+        <v>520889</v>
       </c>
       <c r="R16" t="n">
-        <v>6847697</v>
+        <v>6847776</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2167,19 +2198,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>19:17</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>19:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2194,44 +2215,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134273567</v>
+        <v>134273573</v>
       </c>
       <c r="B17" t="n">
-        <v>79461</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2241,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520974</v>
+        <v>520916</v>
       </c>
       <c r="R17" t="n">
-        <v>6847722</v>
+        <v>6847759</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2276,7 +2297,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2286,12 +2307,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Högstubbe med kulturspår och varglav.</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2318,32 +2334,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134267152</v>
+        <v>134267874</v>
       </c>
       <c r="B18" t="n">
-        <v>79461</v>
+        <v>79397</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>967</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2353,10 +2369,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520881</v>
+        <v>520826</v>
       </c>
       <c r="R18" t="n">
-        <v>6847688</v>
+        <v>6847798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2389,11 +2405,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt på grov gammal silverhögstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2420,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134273542</v>
+        <v>117398799</v>
       </c>
       <c r="B19" t="n">
-        <v>79461</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2431,37 +2442,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520761</v>
+        <v>520859</v>
       </c>
       <c r="R19" t="n">
-        <v>6847669</v>
+        <v>6847728</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2485,22 +2500,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:42</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:42</t>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2515,22 +2525,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134273573</v>
+        <v>134267359</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,37 +2548,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520916</v>
+        <v>520900</v>
       </c>
       <c r="R20" t="n">
-        <v>6847759</v>
+        <v>6847679</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2595,19 +2605,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>19:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,15 +2622,306 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134267335</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>520898</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6847679</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134266290</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>520788</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6847808</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134267296</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyrorna, Slåttkölsmyrorna, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>520886</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6847676</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18098-2024 artfynd.xlsx
+++ b/artfynd/A 18098-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134266572</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398708</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398714</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267152</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267700</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273537</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273538</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1607,6 +1652,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273542</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273564</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273565</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1933,6 +1993,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273567</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267652</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2127,6 +2197,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267687</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2224,6 +2299,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267735</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2331,6 +2411,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273573</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2428,6 +2513,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267874</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2534,6 +2624,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398799</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2631,6 +2726,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267359</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2728,6 +2828,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267335</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2825,6 +2930,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134266290</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2922,8 +3032,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267296</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>